--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742601</v>
       </c>
       <c r="B2" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129742601</v>
+        <v>127924421</v>
       </c>
       <c r="B2" t="n">
-        <v>97701</v>
+        <v>58826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,59 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Smedjebacken Västansjö 1:43, Dlr</t>
+          <t>Smedjebacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521043</v>
+        <v>520664</v>
       </c>
       <c r="R2" t="n">
-        <v>6662980</v>
+        <v>6662537</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,12 +765,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,10 +791,455 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Elliot Örjes, Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127923705</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>520658</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6662538</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Positivt svar på eDNA-analys av vatten taget på lokalen.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elliot Örjes, Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127925976</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520659</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6662535</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elliot Örjes, Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127926332</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520657</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6662537</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stor mängd yngel, art bekräftad via eDNA.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elliot Örjes, Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129742601</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Halvvägsdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>521043</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6662980</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Caspar Ström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39832-2024 artfynd.xlsx
+++ b/artfynd/A 39832-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127924421</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127923705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127925976</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127926332</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,8 +1265,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>